--- a/output/pdf_financials_xlsx/FFF.xlsx
+++ b/output/pdf_financials_xlsx/FFF.xlsx
@@ -673,13 +673,13 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.783473</v>
+        <v>-0.783473</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="17">
@@ -749,13 +749,13 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.783473</v>
+        <v>-0.783473</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="21">
@@ -797,13 +797,13 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.783473</v>
+        <v>-0.783473</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="24">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-12.411533</v>
+        <v>12.411533</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-20.020562</v>
+        <v>20.020562</v>
       </c>
     </row>
     <row r="27">
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.783473</v>
+        <v>-0.783473</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="28">
@@ -895,13 +895,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.783473</v>
+        <v>-0.783473</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="30">
@@ -933,13 +933,13 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0.4098</v>
+        <v>2.7745</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.4098</v>
+        <v>1.104223</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.985765</v>
+        <v>2.084698</v>
       </c>
     </row>
     <row r="93">
@@ -2057,7 +2057,7 @@
         <v>-0.744692</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="100">
@@ -3035,7 +3035,11 @@
           <t>Warrant reserve</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
         <v>2.3647</v>
       </c>
@@ -4067,10 +4071,10 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>4.804935</v>
+        <v>-4.804935</v>
       </c>
     </row>
     <row r="46">
@@ -4519,10 +4523,10 @@
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0.783473</v>
+        <v>-0.783473</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>0.744692</v>
+        <v>-0.744692</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/FFF.xlsx
+++ b/output/pdf_financials_xlsx/FFF.xlsx
@@ -978,7 +978,7 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.08506</v>
       </c>
       <c r="C34" s="3" t="n">
         <v>0.066528</v>
@@ -1010,7 +1010,7 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.08506</v>
       </c>
       <c r="C36" s="3" t="n">
         <v>0.066528</v>
@@ -3161,7 +3161,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E16" s="5" t="n">
